--- a/Team-Data/2013-14/12-19-2013-14.xlsx
+++ b/Team-Data/2013-14/12-19-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -796,7 +863,7 @@
         <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>24</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1139,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
         <v>16</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
@@ -1306,7 +1373,7 @@
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
@@ -1321,13 +1388,13 @@
         <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1389,64 +1456,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.36</v>
+        <v>0.375</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
       </c>
       <c r="I6" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="L6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M6" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T6" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U6" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="W6" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X6" t="n">
         <v>4.8</v>
@@ -1455,40 +1522,40 @@
         <v>6.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1497,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
         <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1536,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>21</v>
@@ -1706,7 +1773,7 @@
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1846,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>9</v>
@@ -2064,7 +2131,7 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2277,7 @@
         <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>5</v>
@@ -2219,7 +2286,7 @@
         <v>13</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
         <v>19</v>
@@ -2264,7 +2331,7 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2299,49 +2366,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519</v>
+        <v>0.538</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="J11" t="n">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.465</v>
       </c>
       <c r="L11" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M11" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.734</v>
+        <v>0.731</v>
       </c>
       <c r="R11" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S11" t="n">
         <v>34.8</v>
@@ -2350,49 +2417,49 @@
         <v>45.5</v>
       </c>
       <c r="U11" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V11" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X11" t="n">
         <v>4.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB11" t="n">
         <v>103</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>16</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
@@ -2413,13 +2480,13 @@
         <v>18</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2428,13 +2495,13 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
         <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2446,7 +2513,7 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>5.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>7.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
         <v>20</v>
@@ -2816,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -2953,10 +3020,10 @@
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>22</v>
@@ -2989,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>20</v>
@@ -3299,13 +3366,13 @@
         <v>20</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3538,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -3866,7 +3933,7 @@
         <v>21</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>17</v>
@@ -4066,7 +4133,7 @@
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>2</v>
@@ -4084,7 +4151,7 @@
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
         <v>11</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4215,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4301,85 +4368,85 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.84</v>
+        <v>0.833</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
         <v>83.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.47</v>
+        <v>0.468</v>
       </c>
       <c r="L22" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M22" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.338</v>
+        <v>0.329</v>
       </c>
       <c r="O22" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="P22" t="n">
-        <v>25.9</v>
+        <v>26.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S22" t="n">
         <v>36.1</v>
       </c>
       <c r="T22" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
         <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
         <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,31 +4458,31 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM22" t="n">
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP22" t="n">
         <v>4</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>6</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -4430,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,16 +4512,16 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>4</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>27</v>
@@ -4773,7 +4840,7 @@
         <v>11</v>
       </c>
       <c r="AN24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
         <v>22</v>
@@ -4794,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5319,7 +5386,7 @@
         <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>6</v>
@@ -5346,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
@@ -5411,67 +5478,67 @@
         <v>41.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491</v>
+        <v>0.493</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="P28" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.748</v>
+        <v>0.751</v>
       </c>
       <c r="R28" t="n">
         <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="V28" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="AB28" t="n">
         <v>103.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5528,7 +5595,7 @@
         <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5738,7 @@
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -5683,7 +5750,7 @@
         <v>13</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>18</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-19-2013-14</t>
+          <t>2013-12-19</t>
         </is>
       </c>
     </row>
